--- a/data/outputs/a_r_9_NEW.xlsx
+++ b/data/outputs/a_r_9_NEW.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,27 +444,37 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>break_minutes</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>h100</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>h125</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>h150</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>shabbat</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>break</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>h100</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>h125</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>h150</t>
         </is>
       </c>
     </row>
@@ -486,12 +496,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -501,29 +511,27 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.00</t>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22/10/2022</t>
+          <t>15/10/2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -538,12 +546,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -553,32 +561,34 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.67</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.00</t>
+          <t>7.67</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>117/00</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>15/10/2022</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>גליליון</t>
@@ -586,12 +596,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00:02</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -601,22 +611,120 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.00</t>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20/10/2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>גליליון</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>22/10/2022</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>גליליון</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
     </row>

--- a/data/outputs/a_r_9_NEW.xlsx
+++ b/data/outputs/a_r_9_NEW.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,7 +444,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>break_minutes</t>
+          <t>break</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -470,11 +470,6 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>shabbat</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>break</t>
         </is>
       </c>
     </row>
@@ -496,12 +491,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -522,11 +517,6 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -546,12 +536,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -572,11 +562,6 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -596,12 +581,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -622,11 +607,6 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -672,11 +652,6 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -696,12 +671,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -722,11 +697,6 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
